--- a/data-vh/Неделя_01.06-07.06_2026_ВХ.xlsx
+++ b/data-vh/Неделя_01.06-07.06_2026_ВХ.xlsx
@@ -2,39 +2,55 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="22320" windowHeight="13176" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Лист_1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Лист_1'!$A$1:$Q$7</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1" refMode="R1C1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
+  <fonts count="3">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Arial"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="8"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4ECC5"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -42,15 +58,149 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCC085"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCC085"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCC085"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCC085"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -125,9 +275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +315,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +349,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +384,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -410,486 +562,539 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Q7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="10.42578125" defaultRowHeight="11.4" customHeight="1"/>
+  <cols>
+    <col width="5.140625" customWidth="1" style="1" min="1" max="1"/>
+    <col width="5.28515625" customWidth="1" style="1" min="2" max="2"/>
+    <col width="3.7109375" customWidth="1" style="1" min="3" max="3"/>
+    <col width="5" customWidth="1" style="1" min="4" max="4"/>
+    <col width="10.140625" customWidth="1" style="1" min="5" max="5"/>
+    <col width="22.5703125" customWidth="1" style="1" min="6" max="6"/>
+    <col width="21" customWidth="1" style="1" min="7" max="7"/>
+    <col width="29.7109375" customWidth="1" style="1" min="8" max="8"/>
+    <col width="18.5703125" customWidth="1" style="1" min="9" max="9"/>
+    <col width="32.140625" customWidth="1" style="1" min="10" max="10"/>
+    <col width="13.7109375" customWidth="1" style="1" min="11" max="11"/>
+    <col width="7.28515625" customWidth="1" style="1" min="12" max="12"/>
+    <col width="8.28515625" customWidth="1" style="1" min="13" max="13"/>
+    <col width="27.5703125" customWidth="1" style="1" min="14" max="14"/>
+    <col width="30.7109375" customWidth="1" style="1" min="15" max="15"/>
+    <col width="74.7109375" customWidth="1" style="1" min="16" max="16"/>
+    <col width="44.28515625" customWidth="1" style="1" min="17" max="17"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="25.95" customHeight="1">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>№ п/п</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Номер</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="22" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Дата</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>Основание</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="18" t="inlineStr">
         <is>
           <t>Поставщик/Переработчик</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="15" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="15" t="inlineStr">
         <is>
           <t>Место проведения контроля</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="15" t="inlineStr">
         <is>
           <t>Номенклатура</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="15" t="inlineStr">
         <is>
           <t>Группа номенклатуры</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="15" t="inlineStr">
         <is>
           <t>Кол., шт.</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="15" t="inlineStr">
         <is>
           <t>Кол., кг</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="15" t="inlineStr">
         <is>
           <t>Вид несоответствия</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="15" t="inlineStr">
         <is>
           <t>Критичность несоответствия</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="15" t="inlineStr">
         <is>
           <t>Несоответствие</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="15" t="inlineStr">
         <is>
           <t>Решение</t>
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" ht="34.95" customHeight="1">
+      <c r="A2" s="3" t="n">
         <v>150</v>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>В00-0000084</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+      <c r="E2" s="16" t="inlineStr">
         <is>
           <t>01.06.2026</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>Монтажторгстрой ООО</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>_Склад корпус №11</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="7" t="inlineStr">
         <is>
           <t>(ПФ(закупка)) Пластина (32х570х2380) (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L2" t="n">
+      <c r="L2" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2" s="10" t="n">
         <v>1546.95</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="7" t="inlineStr">
         <is>
           <t>Несоответствие требованиям КД</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="7" t="inlineStr">
         <is>
           <t>Размер 2380+-2мм, фактически 2384мм (1шт). Отсутствует кромка 20+-0,3*3+-1.Размер 55+-0,4мм, фактически 53,69-56,81мм. Заусенцы. Остатки силиконового герметика..</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами работников УМИ</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" ht="34.95" customHeight="1">
+      <c r="A3" s="3" t="n">
         <v>151</v>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="16" t="inlineStr">
         <is>
           <t>В00-0000085</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="C3" s="21" t="n"/>
+      <c r="D3" s="22" t="n"/>
+      <c r="E3" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000285 от 02.06.2026 9:21:20</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>АСТРЕЯ ООО (ЭДО Такском ЗП согл. от 19.03.2025)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J3" s="7" t="inlineStr">
         <is>
           <t>ПФК(закупка) Элемент закладной ЗФ-30/4/К300-4,5  (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>ОО</t>
         </is>
       </c>
-      <c r="L3" t="n">
+      <c r="L3" s="3" t="n">
         <v>14</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3" s="14" t="n">
         <v>3058.3</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N3" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O3" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P3" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 14771: ширина сварного шва С17 12+-2мм, фактически 6,4-15,4мм, высота сварного шва С17 1+-1мм, фактически до -0,77мм. Подрез (1шт). Натеки металла сварного шва У4 (1шт).</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены силами переработчика</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" ht="22.95" customHeight="1">
+      <c r="A4" s="3" t="n">
         <v>152</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="16" t="inlineStr">
         <is>
           <t>В00-0000086</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="21" t="n"/>
+      <c r="D4" s="22" t="n"/>
+      <c r="E4" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="19" t="inlineStr">
         <is>
           <t>Приобретение товаров и услуг 0000-001983 от 14.05.2026 0:00:00</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="20" t="inlineStr">
         <is>
           <t>Поставщик</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>МЕТАЛЛСЕРВИС-МОСКВА ООО</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>Корпус №13</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J4" s="7" t="inlineStr">
         <is>
           <t>_уу_Полоса 5,0*30*6000 ГОСТ 103-2006/ Ст3сп</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="K4" s="7" t="inlineStr">
         <is>
           <t>Листы сталь Ст3сп, Ст3сп5 (С255, Ст2сп)</t>
         </is>
       </c>
-      <c r="L4" t="n">
+      <c r="L4" s="3" t="n">
         <v>59</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4" s="11" t="n">
         <v>417.012</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="N4" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="O4" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  В лом;</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="P4" s="7" t="inlineStr">
         <is>
           <t>По ГОСТ 103 длина 6000+50 мм, фактически 875-6000 мм. Имеются дефекты ввиде перегиба (загиба, залома).</t>
         </is>
       </c>
+      <c r="Q4" s="7" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" ht="70.95" customHeight="1">
+      <c r="A5" s="3" t="n">
         <v>153</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>В00-0000087</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="C5" s="21" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="19" t="inlineStr">
         <is>
           <t>Поступление от переработчика 0000-000269 от 30.05.2026 16:35:59</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>ВИНПЛАСТ ООО (ЭДО Такском ЗП увед. с 23.05.25)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>Склад ПДС черный</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J5" s="7" t="inlineStr">
         <is>
           <t>(ПФК(закупка)) Настил SP 34х38/25х2 S4 А 730х750 (от поставщика/переработчика)</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="K5" s="7" t="inlineStr">
         <is>
           <t>Настилы сварные</t>
         </is>
       </c>
-      <c r="L5" t="n">
+      <c r="L5" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5" s="8" t="n">
         <v>243.6</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="N5" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="O5" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="P5" s="7" t="inlineStr">
         <is>
           <t>Выступание связующих элементов по СТО не более 1,5мм, фактически до 5мм. Занижение обрамляющего элемента по СТО не более 1мм, фактически до 5мм. Выступание обрамляющего элемента по СТО не более 1мм, фактически до 3мм. Выгнутость по СТО не более 8мм, фактически до 11мм. Механические повреждения. Дефекты сварных швов: брызги металла, кратеры, поры, натёки, прожоги, несплавления.</t>
         </is>
       </c>
+      <c r="Q5" s="7" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" ht="58.95" customHeight="1">
+      <c r="A6" s="3" t="n">
         <v>154</v>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>В00-0000088</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="C6" s="21" t="n"/>
+      <c r="D6" s="22" t="n"/>
+      <c r="E6" s="16" t="inlineStr">
         <is>
           <t>02.06.2026</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="I6" s="7" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="K6" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L6" t="n">
+      <c r="L6" s="3" t="n">
         <v>10</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6" s="8" t="n">
         <v>731.2</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N6" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O6" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P6" s="7" t="inlineStr">
         <is>
           <t>1.На локальных участках дефекты сварных швов: брызги металла, плохое повторное возбуждение дуги. Доработано в процессе контроля сотрудником ОА «Завод Продмаш».    2.Разнооттеночность очищенной поверхности от светло-серого до темно-серого цвета, на торцевых поверхностях деталей и отверстий «бурая ржавчина».     Шероховатость поверхности Rz от 30 до 80 мкм.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Q6" s="7" t="inlineStr">
         <is>
           <t>Несоответствия устранены</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
+    <row r="7" ht="46.95" customHeight="1">
+      <c r="A7" s="3" t="n">
         <v>155</v>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>В00-0000089</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="C7" s="21" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="16" t="inlineStr">
         <is>
           <t>03.06.2026</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="6" t="inlineStr">
         <is>
           <t>Переработчик</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>ТЗМИК АЛЬТАИР ООО</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>ГПОкр(240) Кронштейн КП</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="K7" s="7" t="inlineStr">
         <is>
           <t>МК, другое</t>
         </is>
       </c>
-      <c r="L7" t="n">
+      <c r="L7" s="3" t="n">
         <v>22</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M7" s="10" t="n">
         <v>1608.64</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="N7" s="7" t="inlineStr">
         <is>
           <t>Невыполнение требований НТД</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="O7" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Устранимое</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="P7" s="7" t="inlineStr">
         <is>
           <t>Дефекты сварных швов:    Поры, плохое повторное возбуждение дуги, отсутствие плавного перехода к основному металлу. Устранено в процессе контроля.     Состояние поверхности:    "бурая ржавчина" на локальных участках.     На двух изделиях шероховатость от 9 до 54 мкм (ср. 33 мкм), от 7 до 54 мкм (ср. 29 мкм)</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Q7" s="7" t="inlineStr">
         <is>
           <t>Проведен контроль после повторной дробеструйной обработки, несоответствия не выявлены</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:Q7">
+    <filterColumn colId="1" hiddenButton="0" showButton="0"/>
+    <filterColumn colId="2" hiddenButton="0" showButton="0"/>
+  </autoFilter>
+  <mergeCells count="7">
+    <mergeCell ref="B3:D3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.3937007874015748" right="0.3937007874015748" top="0.3937007874015748" bottom="0.3937007874015748" header="0" footer="0"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" pageOrder="overThenDown"/>
 </worksheet>
 </file>